--- a/results/tables/xgboost_metrics.xlsx
+++ b/results/tables/xgboost_metrics.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,20 +456,25 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>SMAPE(%)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>±10%准确率(%)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>±15%准确率(%)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>±20%准确率(%)</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>RPD</t>
         </is>
@@ -482,31 +487,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>26.22763061523438</v>
+        <v>30.4609432220459</v>
       </c>
       <c r="C2" t="n">
-        <v>35.33197402738595</v>
+        <v>40.56699585061421</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9946051836013794</v>
+        <v>0.9927515983581543</v>
       </c>
       <c r="E2" t="n">
-        <v>20.92566586152095</v>
+        <v>27.6565137593558</v>
       </c>
       <c r="F2" t="n">
-        <v>69.45945945945947</v>
-      </c>
-      <c r="G2" t="inlineStr">
+        <v>23.31733595615024</v>
+      </c>
+      <c r="G2" t="n">
+        <v>67.66304347826086</v>
+      </c>
+      <c r="H2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -519,33 +527,36 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>121.098388671875</v>
+        <v>89.06491088867188</v>
       </c>
       <c r="C3" t="n">
-        <v>208.5150155714211</v>
+        <v>146.7226270786991</v>
       </c>
       <c r="D3" t="n">
-        <v>0.834057629108429</v>
+        <v>0.9230362772941589</v>
       </c>
       <c r="E3" t="n">
-        <v>59.52683585233491</v>
+        <v>24.27082643840675</v>
       </c>
       <c r="F3" t="n">
-        <v>31.46067415730337</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>43.8</t>
-        </is>
+        <v>36.28773120244553</v>
+      </c>
+      <c r="G3" t="n">
+        <v>38.46153846153847</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>53.9</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>60.4</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>3.60</t>
         </is>
       </c>
     </row>

--- a/results/tables/xgboost_metrics.xlsx
+++ b/results/tables/xgboost_metrics.xlsx
@@ -425,139 +425,102 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>数据集</t>
+          <t>指标</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>MAE(kWh)</t>
+          <t>Mean</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>RMSE(kWh)</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>R2</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>MAPE(%)</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>SMAPE(%)</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>±10%准确率(%)</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>±15%准确率(%)</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>±20%准确率(%)</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>RPD</t>
+          <t>Std</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>训练集</t>
+          <t>MAE(kWh)</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>30.4609432220459</v>
+        <v>252.632</v>
       </c>
       <c r="C2" t="n">
-        <v>40.56699585061421</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.9927515983581543</v>
-      </c>
-      <c r="E2" t="n">
-        <v>27.6565137593558</v>
-      </c>
-      <c r="F2" t="n">
-        <v>23.31733595615024</v>
-      </c>
-      <c r="G2" t="n">
-        <v>67.66304347826086</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>121.8586117688127</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>测试集</t>
+          <t>RMSE(kWh)</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>89.06491088867188</v>
+        <v>345.146</v>
       </c>
       <c r="C3" t="n">
-        <v>146.7226270786991</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0.9230362772941589</v>
-      </c>
-      <c r="E3" t="n">
-        <v>24.27082643840675</v>
-      </c>
-      <c r="F3" t="n">
-        <v>36.28773120244553</v>
-      </c>
-      <c r="G3" t="n">
-        <v>38.46153846153847</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>49.5</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>60.4</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
+        <v>165.0294824299922</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.4066000000000001</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.2576674040524162</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>MAPE(%)</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>46.528</v>
+      </c>
+      <c r="C5" t="n">
+        <v>9.710158254803746</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SMAPE(%)</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>64.68999999999998</v>
+      </c>
+      <c r="C6" t="n">
+        <v>14.4777231174887</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>RPD</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1.442</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.4933738722082655</v>
       </c>
     </row>
   </sheetData>

--- a/results/tables/xgboost_metrics.xlsx
+++ b/results/tables/xgboost_metrics.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,12 +436,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Mean</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Std</t>
+          <t>值</t>
         </is>
       </c>
     </row>
@@ -452,10 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>252.632</v>
-      </c>
-      <c r="C2" t="n">
-        <v>121.8586117688127</v>
+        <v>82.53</v>
       </c>
     </row>
     <row r="3">
@@ -465,10 +457,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>345.146</v>
-      </c>
-      <c r="C3" t="n">
-        <v>165.0294824299922</v>
+        <v>120.73</v>
       </c>
     </row>
     <row r="4">
@@ -478,10 +467,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.4066000000000001</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0.2576674040524162</v>
+        <v>0.9333</v>
       </c>
     </row>
     <row r="5">
@@ -491,10 +477,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>46.528</v>
-      </c>
-      <c r="C5" t="n">
-        <v>9.710158254803746</v>
+        <v>32.93</v>
       </c>
     </row>
     <row r="6">
@@ -504,10 +487,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>64.68999999999998</v>
-      </c>
-      <c r="C6" t="n">
-        <v>14.4777231174887</v>
+        <v>30.26</v>
       </c>
     </row>
     <row r="7">
@@ -517,10 +497,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.442</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0.4933738722082655</v>
+        <v>3.87</v>
       </c>
     </row>
   </sheetData>

--- a/results/tables/xgboost_metrics.xlsx
+++ b/results/tables/xgboost_metrics.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -443,61 +443,61 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MAE(kWh)</t>
+          <t>MAE_residual(kW)</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>82.53</v>
+        <v>59.47</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>RMSE(kWh)</t>
+          <t>RMSE_residual(kW)</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>120.73</v>
+        <v>83.76000000000001</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R²_residual</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9333</v>
+        <v>0.5427999999999999</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MAPE(%)</t>
+          <t>特征维度</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>32.93</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SMAPE(%)</t>
+          <t>训练样本</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>30.26</v>
+        <v>384</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>RPD</t>
+          <t>测试样本</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.87</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>
